--- a/Result/profitability/1815.xlsx
+++ b/Result/profitability/1815.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>0.36125</v>
+        <v>0.54625</v>
       </c>
       <c r="N2" t="n">
-        <v>27.92</v>
+        <v>30.70625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>0.37875</v>
+        <v>0.5225000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>29.02875</v>
+        <v>31.10375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.40375</v>
+        <v>0.54375</v>
       </c>
       <c r="N4" t="n">
-        <v>27.95125</v>
+        <v>29.23125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.36</v>
+        <v>0.5487500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>25.81125</v>
+        <v>27.73875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>0.28875</v>
+        <v>0.4025</v>
       </c>
       <c r="N6" t="n">
-        <v>21.58375</v>
+        <v>23.22125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1725</v>
+        <v>0.24875</v>
       </c>
       <c r="N7" t="n">
-        <v>19.26375</v>
+        <v>20.63375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07250000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="N8" t="n">
-        <v>17.94</v>
+        <v>18.44</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2131</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1279</v>
+      </c>
+      <c r="E75" t="n">
+        <v>852</v>
+      </c>
+      <c r="F75" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>548</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>25.69%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>408</v>
+      </c>
+      <c r="J75" t="n">
+        <v>955</v>
+      </c>
+      <c r="K75" t="n">
+        <v>843</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.39375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8354430379746833</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1112037809285515</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-25.16666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6281059063136456</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
